--- a/static/standards-correlations/Oklahoma_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Oklahoma_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$32</definedName>
@@ -550,10 +550,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | OAS-CS February 2023 | Level 1 = all students, grades 9-10</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | OAS-CS February 2023 | Level 1 = all students, grades 9-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -587,7 +588,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -713,7 +714,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Develop and apply criteria for the systematic discovery of errors and systematic strategies for the correction of errors in computing systems.</t>
+          <t>Develop and apply criteria for the systematic introductory of errors and systematic strategies for the correction of errors in computing systems.</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -738,7 +739,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Oklahoma asks for both discovery AND correction strategies, applied systematically. A structured debugging process is a stated objective of Unit 1.1, and students must separate a code fault from a wiring or mechanical fault before acting.</t>
+          <t>Oklahoma asks for both introductory AND correction strategies, applied systematically. A structured debugging process is a stated objective of Unit 1.1, and students must separate a code fault from a wiring or mechanical fault before acting.</t>
         </is>
       </c>
     </row>
@@ -785,7 +786,7 @@
       </c>
       <c r="I8" s="8" t="inlineStr">
         <is>
-          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Discovery Systems 9 covers protocols conceptually. Routers, switches, IP and DNS are not covered, so this is the weakest standard in the Oklahoma file.</t>
+          <t>Ext 5.3F (Talking to a Server) introduces the server as a distinct role and Introductory Systems 9 covers protocols conceptually. Routers, switches, IP and DNS are not covered, so this is the weakest standard in the Oklahoma file.</t>
         </is>
       </c>
     </row>
@@ -1517,7 +1518,7 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 4 teaches flowchart symbols and decision points, Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram of the student's own program, and Ext 5.1G (Write the Guide) plus Ext 5.3A (Write a Real README) supply the documentation.</t>
+          <t>Introductory Systems 4 teaches flowchart symbols and decision points, Ext 1.2B (Dependency Map) produces a node-and-arrow structure diagram of the student's own program, and Ext 5.1G (Write the Guide) plus Ext 5.3A (Write a Real README) supply the documentation.</t>
         </is>
       </c>
     </row>
@@ -1915,6 +1916,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
@@ -1959,7 +1961,7 @@
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1973,7 @@
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2071,6 +2073,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
@@ -2094,7 +2098,7 @@
   L1.AP.PD.05 allows user-friendly, efficient AND/OR accessible, so accessibility being uncovered does not cost the standard.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.</t>
         </is>
       </c>
